--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121204063</v>
+        <v>121204008</v>
       </c>
       <c r="B7" t="n">
-        <v>97031</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,39 +1231,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490838</v>
+        <v>491131</v>
       </c>
       <c r="R7" t="n">
-        <v>6953766</v>
+        <v>6954046</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121204016</v>
+        <v>121204097</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491105</v>
+        <v>490892</v>
       </c>
       <c r="R8" t="n">
-        <v>6953940</v>
+        <v>6953702</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204097</v>
+        <v>121204000</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,26 +1447,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490892</v>
+        <v>490957</v>
       </c>
       <c r="R9" t="n">
-        <v>6953702</v>
+        <v>6954066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,13 +1517,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121204091</v>
+        <v>121204083</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490874</v>
+        <v>490859</v>
       </c>
       <c r="R10" t="n">
-        <v>6953727</v>
+        <v>6953753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121203988</v>
+        <v>121204063</v>
       </c>
       <c r="B11" t="n">
-        <v>79679</v>
+        <v>97041</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,30 +1664,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1695,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491112</v>
+        <v>490838</v>
       </c>
       <c r="R11" t="n">
-        <v>6954274</v>
+        <v>6953766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204083</v>
+        <v>121204016</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490859</v>
+        <v>491105</v>
       </c>
       <c r="R12" t="n">
-        <v>6953753</v>
+        <v>6953940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121204000</v>
+        <v>121204091</v>
       </c>
       <c r="B13" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,31 +1889,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490957</v>
+        <v>490874</v>
       </c>
       <c r="R13" t="n">
-        <v>6954066</v>
+        <v>6953727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,17 +1954,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>121204011</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121204008</v>
+        <v>121203988</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491131</v>
+        <v>491112</v>
       </c>
       <c r="R15" t="n">
-        <v>6954046</v>
+        <v>6954274</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121204008</v>
+        <v>121204083</v>
       </c>
       <c r="B7" t="n">
         <v>78601</v>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491131</v>
+        <v>490859</v>
       </c>
       <c r="R7" t="n">
-        <v>6954046</v>
+        <v>6953753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121204097</v>
+        <v>121204063</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>97041</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,30 +1337,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490892</v>
+        <v>490838</v>
       </c>
       <c r="R8" t="n">
-        <v>6953702</v>
+        <v>6953766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204000</v>
+        <v>121204011</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,31 +1456,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1479,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490957</v>
+        <v>491121</v>
       </c>
       <c r="R9" t="n">
-        <v>6954066</v>
+        <v>6953974</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,17 +1521,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121204083</v>
+        <v>121203988</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490859</v>
+        <v>491112</v>
       </c>
       <c r="R10" t="n">
-        <v>6953753</v>
+        <v>6954274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121204063</v>
+        <v>121204097</v>
       </c>
       <c r="B11" t="n">
-        <v>97041</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,39 +1664,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1704,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490838</v>
+        <v>490892</v>
       </c>
       <c r="R11" t="n">
-        <v>6953766</v>
+        <v>6953702</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1758,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204016</v>
+        <v>121204008</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1810,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491105</v>
+        <v>491131</v>
       </c>
       <c r="R12" t="n">
-        <v>6953940</v>
+        <v>6954046</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121204091</v>
+        <v>121204000</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,26 +1880,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490874</v>
+        <v>490957</v>
       </c>
       <c r="R13" t="n">
-        <v>6953727</v>
+        <v>6954066</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,13 +1950,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204011</v>
+        <v>121204091</v>
       </c>
       <c r="B14" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491121</v>
+        <v>490874</v>
       </c>
       <c r="R14" t="n">
-        <v>6953974</v>
+        <v>6953727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121203988</v>
+        <v>121204016</v>
       </c>
       <c r="B15" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491112</v>
+        <v>491105</v>
       </c>
       <c r="R15" t="n">
-        <v>6954274</v>
+        <v>6953940</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>121204083</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121204063</v>
+        <v>121204008</v>
       </c>
       <c r="B8" t="n">
-        <v>97041</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,39 +1337,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1377,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490838</v>
+        <v>491131</v>
       </c>
       <c r="R8" t="n">
-        <v>6953766</v>
+        <v>6954046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204011</v>
+        <v>121204063</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>97054</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,30 +1443,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491121</v>
+        <v>490838</v>
       </c>
       <c r="R9" t="n">
-        <v>6953974</v>
+        <v>6953766</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121203988</v>
+        <v>121204091</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491112</v>
+        <v>490874</v>
       </c>
       <c r="R10" t="n">
-        <v>6954274</v>
+        <v>6953727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1655,7 @@
         <v>121204097</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204008</v>
+        <v>121204016</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491131</v>
+        <v>491105</v>
       </c>
       <c r="R12" t="n">
-        <v>6954046</v>
+        <v>6953940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121204000</v>
+        <v>121203988</v>
       </c>
       <c r="B13" t="n">
-        <v>57367</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,31 +1880,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490957</v>
+        <v>491112</v>
       </c>
       <c r="R13" t="n">
-        <v>6954066</v>
+        <v>6954274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,17 +1945,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1979,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204091</v>
+        <v>121204011</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490874</v>
+        <v>491121</v>
       </c>
       <c r="R14" t="n">
-        <v>6953727</v>
+        <v>6953974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121204016</v>
+        <v>121204000</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,26 +2092,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2128,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491105</v>
+        <v>490957</v>
       </c>
       <c r="R15" t="n">
-        <v>6953940</v>
+        <v>6954066</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,13 +2162,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121204083</v>
+        <v>121204016</v>
       </c>
       <c r="B7" t="n">
         <v>78604</v>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490859</v>
+        <v>491105</v>
       </c>
       <c r="R7" t="n">
-        <v>6953753</v>
+        <v>6953940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121204008</v>
+        <v>121204091</v>
       </c>
       <c r="B8" t="n">
         <v>78604</v>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491131</v>
+        <v>490874</v>
       </c>
       <c r="R8" t="n">
-        <v>6954046</v>
+        <v>6953727</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204063</v>
+        <v>121204097</v>
       </c>
       <c r="B9" t="n">
-        <v>97054</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,39 +1443,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490838</v>
+        <v>490892</v>
       </c>
       <c r="R9" t="n">
-        <v>6953766</v>
+        <v>6953702</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121204091</v>
+        <v>121204063</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>97055</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,30 +1549,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490874</v>
+        <v>490838</v>
       </c>
       <c r="R10" t="n">
-        <v>6953727</v>
+        <v>6953766</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121204097</v>
+        <v>121203988</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,21 +1668,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490892</v>
+        <v>491112</v>
       </c>
       <c r="R11" t="n">
-        <v>6953702</v>
+        <v>6954274</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204016</v>
+        <v>121204011</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491105</v>
+        <v>491121</v>
       </c>
       <c r="R12" t="n">
-        <v>6953940</v>
+        <v>6953974</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121203988</v>
+        <v>121204008</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491112</v>
+        <v>491131</v>
       </c>
       <c r="R13" t="n">
-        <v>6954274</v>
+        <v>6954046</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204011</v>
+        <v>121204000</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,26 +1986,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2013,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491121</v>
+        <v>490957</v>
       </c>
       <c r="R14" t="n">
-        <v>6953974</v>
+        <v>6954066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,13 +2056,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2076,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121204000</v>
+        <v>121204083</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,31 +2101,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2124,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490957</v>
+        <v>490859</v>
       </c>
       <c r="R15" t="n">
-        <v>6954066</v>
+        <v>6953753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,17 +2166,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121204016</v>
+        <v>121204000</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,26 +1235,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491105</v>
+        <v>490957</v>
       </c>
       <c r="R7" t="n">
-        <v>6953940</v>
+        <v>6954066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,13 +1305,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121204091</v>
+        <v>121204097</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490874</v>
+        <v>490892</v>
       </c>
       <c r="R8" t="n">
-        <v>6953727</v>
+        <v>6953702</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204097</v>
+        <v>121204091</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490892</v>
+        <v>490874</v>
       </c>
       <c r="R9" t="n">
-        <v>6953702</v>
+        <v>6953727</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,7 +1549,7 @@
         <v>121204063</v>
       </c>
       <c r="B10" t="n">
-        <v>97055</v>
+        <v>97058</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1655,7 +1664,7 @@
         <v>121203988</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204011</v>
+        <v>121204016</v>
       </c>
       <c r="B12" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1783,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1801,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491121</v>
+        <v>491105</v>
       </c>
       <c r="R12" t="n">
-        <v>6953974</v>
+        <v>6953940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,7 +1876,7 @@
         <v>121204008</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204000</v>
+        <v>121204011</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>79688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,31 +1995,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490957</v>
+        <v>491121</v>
       </c>
       <c r="R14" t="n">
-        <v>6954066</v>
+        <v>6953974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,17 +2060,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>121204083</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121204097</v>
+        <v>121203988</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490892</v>
+        <v>491112</v>
       </c>
       <c r="R8" t="n">
-        <v>6953702</v>
+        <v>6954274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204091</v>
+        <v>121204063</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>97058</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,30 +1452,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490874</v>
+        <v>490838</v>
       </c>
       <c r="R9" t="n">
-        <v>6953727</v>
+        <v>6953766</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121204063</v>
+        <v>121204083</v>
       </c>
       <c r="B10" t="n">
-        <v>97058</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1558,39 +1567,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490838</v>
+        <v>490859</v>
       </c>
       <c r="R10" t="n">
-        <v>6953766</v>
+        <v>6953753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121203988</v>
+        <v>121204011</v>
       </c>
       <c r="B11" t="n">
         <v>79688</v>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491112</v>
+        <v>491121</v>
       </c>
       <c r="R11" t="n">
-        <v>6954274</v>
+        <v>6953974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204016</v>
+        <v>121204091</v>
       </c>
       <c r="B12" t="n">
         <v>78607</v>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491105</v>
+        <v>490874</v>
       </c>
       <c r="R12" t="n">
-        <v>6953940</v>
+        <v>6953727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121204008</v>
+        <v>121204016</v>
       </c>
       <c r="B13" t="n">
         <v>78607</v>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491131</v>
+        <v>491105</v>
       </c>
       <c r="R13" t="n">
-        <v>6954046</v>
+        <v>6953940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204011</v>
+        <v>121204008</v>
       </c>
       <c r="B14" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491121</v>
+        <v>491131</v>
       </c>
       <c r="R14" t="n">
-        <v>6953974</v>
+        <v>6954046</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121204083</v>
+        <v>121204097</v>
       </c>
       <c r="B15" t="n">
         <v>78607</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490859</v>
+        <v>490892</v>
       </c>
       <c r="R15" t="n">
-        <v>6953753</v>
+        <v>6953702</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121204000</v>
+        <v>121204091</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,31 +1235,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490957</v>
+        <v>490874</v>
       </c>
       <c r="R7" t="n">
-        <v>6954066</v>
+        <v>6953727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,17 +1300,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,7 +1328,7 @@
         <v>121203988</v>
       </c>
       <c r="B8" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,7 +1434,7 @@
         <v>121204063</v>
       </c>
       <c r="B9" t="n">
-        <v>97058</v>
+        <v>97064</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121204083</v>
+        <v>121204016</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490859</v>
+        <v>491105</v>
       </c>
       <c r="R10" t="n">
-        <v>6953753</v>
+        <v>6953940</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121204011</v>
+        <v>121204000</v>
       </c>
       <c r="B11" t="n">
-        <v>79688</v>
+        <v>57371</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,26 +1668,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491121</v>
+        <v>490957</v>
       </c>
       <c r="R11" t="n">
-        <v>6953974</v>
+        <v>6954066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,13 +1738,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204091</v>
+        <v>121204097</v>
       </c>
       <c r="B12" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490874</v>
+        <v>490892</v>
       </c>
       <c r="R12" t="n">
-        <v>6953727</v>
+        <v>6953702</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121204016</v>
+        <v>121204008</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491105</v>
+        <v>491131</v>
       </c>
       <c r="R13" t="n">
-        <v>6953940</v>
+        <v>6954046</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204008</v>
+        <v>121204011</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491131</v>
+        <v>491121</v>
       </c>
       <c r="R14" t="n">
-        <v>6954046</v>
+        <v>6953974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121204097</v>
+        <v>121204083</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490892</v>
+        <v>490859</v>
       </c>
       <c r="R15" t="n">
-        <v>6953702</v>
+        <v>6953753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121204091</v>
+        <v>121204000</v>
       </c>
       <c r="B7" t="n">
-        <v>78608</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,26 +1235,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490874</v>
+        <v>490957</v>
       </c>
       <c r="R7" t="n">
-        <v>6953727</v>
+        <v>6954066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,13 +1305,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121203988</v>
+        <v>121204097</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491112</v>
+        <v>490892</v>
       </c>
       <c r="R8" t="n">
-        <v>6954274</v>
+        <v>6953702</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204063</v>
+        <v>121204008</v>
       </c>
       <c r="B9" t="n">
-        <v>97064</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,39 +1452,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490838</v>
+        <v>491131</v>
       </c>
       <c r="R9" t="n">
-        <v>6953766</v>
+        <v>6954046</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>121204016</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121204000</v>
+        <v>121204011</v>
       </c>
       <c r="B11" t="n">
-        <v>57371</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,31 +1668,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1700,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490957</v>
+        <v>491121</v>
       </c>
       <c r="R11" t="n">
-        <v>6954066</v>
+        <v>6953974</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,17 +1733,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1767,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204097</v>
+        <v>121204063</v>
       </c>
       <c r="B12" t="n">
-        <v>78608</v>
+        <v>97065</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,30 +1770,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490892</v>
+        <v>490838</v>
       </c>
       <c r="R12" t="n">
-        <v>6953702</v>
+        <v>6953766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121204008</v>
+        <v>121203988</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491131</v>
+        <v>491112</v>
       </c>
       <c r="R13" t="n">
-        <v>6954046</v>
+        <v>6954274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204011</v>
+        <v>121204083</v>
       </c>
       <c r="B14" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,21 +1995,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491121</v>
+        <v>490859</v>
       </c>
       <c r="R14" t="n">
-        <v>6953974</v>
+        <v>6953753</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121204083</v>
+        <v>121204091</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490859</v>
+        <v>490874</v>
       </c>
       <c r="R15" t="n">
-        <v>6953753</v>
+        <v>6953727</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 45424-2024 artfynd.xlsx
+++ b/artfynd/A 45424-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121204000</v>
+        <v>121204011</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,31 +1235,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490957</v>
+        <v>491121</v>
       </c>
       <c r="R7" t="n">
-        <v>6954066</v>
+        <v>6953974</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,17 +1300,13 @@
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Endast hört</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1334,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121204097</v>
+        <v>121204063</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>97065</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1346,30 +1337,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490892</v>
+        <v>490838</v>
       </c>
       <c r="R8" t="n">
-        <v>6953702</v>
+        <v>6953766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121204008</v>
+        <v>121204091</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491131</v>
+        <v>490874</v>
       </c>
       <c r="R9" t="n">
-        <v>6954046</v>
+        <v>6953727</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121204016</v>
+        <v>121204000</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,26 +1562,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491105</v>
+        <v>490957</v>
       </c>
       <c r="R10" t="n">
-        <v>6953940</v>
+        <v>6954066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,13 +1632,17 @@
           <t>2024-11-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Endast hört</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1652,7 +1661,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121204011</v>
+        <v>121203988</v>
       </c>
       <c r="B11" t="n">
         <v>79690</v>
@@ -1695,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491121</v>
+        <v>491112</v>
       </c>
       <c r="R11" t="n">
-        <v>6953974</v>
+        <v>6954274</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121204063</v>
+        <v>121204016</v>
       </c>
       <c r="B12" t="n">
-        <v>97065</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,39 +1779,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490838</v>
+        <v>491105</v>
       </c>
       <c r="R12" t="n">
-        <v>6953766</v>
+        <v>6953940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121203988</v>
+        <v>121204083</v>
       </c>
       <c r="B13" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491112</v>
+        <v>490859</v>
       </c>
       <c r="R13" t="n">
-        <v>6954274</v>
+        <v>6953753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121204083</v>
+        <v>121204097</v>
       </c>
       <c r="B14" t="n">
         <v>78609</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490859</v>
+        <v>490892</v>
       </c>
       <c r="R14" t="n">
-        <v>6953753</v>
+        <v>6953702</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121204091</v>
+        <v>121204008</v>
       </c>
       <c r="B15" t="n">
         <v>78609</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490874</v>
+        <v>491131</v>
       </c>
       <c r="R15" t="n">
-        <v>6953727</v>
+        <v>6954046</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
